--- a/data/trans_orig/IP16A03-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36112</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>16834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21372</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>25915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>31896</t>
+          <t>31919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36997</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>33863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68534</t>
+          <t>68521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75079</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6441</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23165</t>
+          <t>23171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>35264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41490</t>
+          <t>41473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>876</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6130</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>11846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18093</t>
+          <t>17945</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23884</t>
+          <t>23217</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98434</t>
+          <t>98512</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106316</t>
+          <t>106286</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>119286</t>
+          <t>119044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>129647</t>
+          <t>129451</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>221146</t>
+          <t>221813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>234097</t>
+          <t>234412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>19206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42459</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>30653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7876</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9824</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1204</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41601</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47439</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>51731</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58240</t>
+          <t>58242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96248</t>
+          <t>96460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104856</t>
+          <t>105444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>98,04%</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22843</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>51845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18188</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127875</t>
+          <t>127196</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>136020</t>
+          <t>135877</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>136389</t>
+          <t>136125</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144673</t>
+          <t>144652</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>267648</t>
+          <t>267473</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>279040</t>
+          <t>279169</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>29145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>33003</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25947</t>
+          <t>26012</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30605</t>
+          <t>30613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7072,7 +7072,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41980</t>
+          <t>41314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>31005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75355</t>
+          <t>75282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80417</t>
+          <t>80425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>20736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48233</t>
+          <t>48434</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>692</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>11307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>117044</t>
+          <t>116906</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>122079</t>
+          <t>122128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106001</t>
+          <t>105728</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>114388</t>
+          <t>114260</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225134</t>
+          <t>225992</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>234796</t>
+          <t>235277</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>22052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29355</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53394</t>
+          <t>53397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9414,7 +9414,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>598</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70815</t>
+          <t>70497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55113</t>
+          <t>55246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123544</t>
+          <t>123571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131179</t>
+          <t>131088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24346</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60360</t>
+          <t>60917</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22067</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>840</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15942</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>167865</t>
+          <t>167727</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174626</t>
+          <t>174547</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>166653</t>
+          <t>167169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>176365</t>
+          <t>176517</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>339334</t>
+          <t>338755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>350014</t>
+          <t>349978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
